--- a/input/EL/parameters.xlsx
+++ b/input/EL/parameters.xlsx
@@ -703,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374841C3-B837-9C4F-8C3E-3E56746FE108}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.1640625" customWidth="1"/>
@@ -1036,6 +1036,16 @@
       </c>
       <c r="B41">
         <v>2018</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LABOUR_SUPPLY_ESTIMATION_PRICE_YEAR</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>2023</v>
       </c>
     </row>
   </sheetData>
